--- a/docs/classifiche/classifica2024.xlsx
+++ b/docs/classifiche/classifica2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel\Desktop\Vs_Code\Sito_Motogp\Sito_Motogp\docs\classifiche\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3E269D-9476-4DA5-BFE6-287B5EB0B6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E73A20-78BE-404F-A341-182F382B048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="3672" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1716" yWindow="2652" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="173">
   <si>
-    <t>2024 STAGIONE 1: MOTO 3</t>
-  </si>
-  <si>
     <t>PILOTA</t>
   </si>
   <si>
@@ -552,6 +549,9 @@
   </si>
   <si>
     <t>1:58.941, pole, FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STAGIONE 2024: MOTO 3</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1024,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="17" t="s">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1161,73 +1161,73 @@
     </row>
     <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="Q6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="R6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R6" s="9" t="s">
+      <c r="S6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="T6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="U6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="9" t="s">
+      <c r="V6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V6" s="9" t="s">
+      <c r="W6" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="W6" s="9" t="s">
-        <v>22</v>
       </c>
       <c r="Y6" s="6">
         <v>6</v>
@@ -1238,14 +1238,14 @@
     </row>
     <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="10">
         <f>Z9 + Z6 + Z11 + Z4 + Z9 +Z9 + Z2 + Z3 +Z3 + Z9 + Z15 + 0.5 + Z6 + Z10 + Z8</f>
         <v>133.5</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6">
         <v>9</v>
@@ -1260,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="10">
         <v>16</v>
@@ -1281,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P7" s="10">
         <v>19</v>
@@ -1305,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y7" s="6">
         <v>7</v>
@@ -1346,14 +1346,14 @@
     </row>
     <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="10">
         <f>Z6 + Z15 + Z3 + Z1 + Z2 + Z6 + Z11 +Z2 + Z4 + Z5 + Z10 + Z1 + Z6 + 8 + Z3 + Z15 + Z6 + Z3</f>
         <v>223</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6">
         <v>6</v>
@@ -1386,13 +1386,13 @@
         <v>5</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O9" s="6">
         <v>10</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="2">
         <v>1</v>
@@ -1455,14 +1455,14 @@
     </row>
     <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="10">
         <f>Z4 + Z3 + Z3 + Z3 +Z5 + Z11 + Z1 +Z2 + Z3 + Z2 + Z12 + Z7 + Z2 + Z1 + Z3</f>
         <v>232</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="6">
         <v>4</v>
@@ -1471,16 +1471,16 @@
         <v>3</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="5">
         <v>3</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="5">
         <v>3</v>
@@ -1510,7 +1510,7 @@
         <v>7</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T11" s="4">
         <v>2</v>
@@ -1564,14 +1564,14 @@
     </row>
     <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="10">
         <f>Z10 + Z15 + Z11 + Z13 + Z12 +Z14 + Z13 + Z13</f>
         <v>27</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="10">
         <v>17</v>
@@ -1595,7 +1595,7 @@
         <v>18</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L13" s="10">
         <v>18</v>
@@ -1607,19 +1607,19 @@
         <v>14</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P13" s="10">
         <v>18</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T13" s="6">
         <v>13</v>
@@ -1628,10 +1628,10 @@
         <v>13</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y13" s="6">
         <v>13</v>
@@ -1673,20 +1673,20 @@
     </row>
     <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="10">
         <f>Z2 + Z2 + Z6 + Z3 +Z8 + Z13 + Z4 +Z5 + Z1 + Z1 + Z8 + Z3 +4.5 + Z4 + Z4 + Z4</f>
         <v>218.5</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -1695,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="5">
         <v>3</v>
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V15" s="6">
         <v>4</v>
@@ -1773,25 +1773,25 @@
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
       <c r="Y16" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="10">
         <f>Z12 + Z12 + Z9 + Z15 + Z15 + Z14</f>
         <v>19</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="10">
         <v>16</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="6">
         <v>12</v>
@@ -1806,10 +1806,10 @@
         <v>15</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L17" s="10">
         <v>17</v>
@@ -1818,10 +1818,10 @@
         <v>18</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17" s="6">
         <v>15</v>
@@ -1833,16 +1833,16 @@
         <v>14</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U17" s="10">
         <v>16</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W17" s="10">
         <v>19</v>
@@ -1875,14 +1875,14 @@
     </row>
     <row r="19" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="10">
         <f>Z11 + Z5 + Z1 + Z1 + Z2 + Z14 + Z9 + Z8 +Z6 + Z5 + Z5 + Z7 + Z4 + Z1 + Z2 + Z5</f>
         <v>213</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="6">
         <v>11</v>
@@ -1894,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="6">
         <v>9</v>
@@ -1930,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T19" s="2">
         <v>1</v>
@@ -1942,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
@@ -1972,17 +1972,17 @@
     </row>
     <row r="21" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="10">
         <f>Z7 + Z6 + Z9 + Z7 + Z13 +Z12 + Z14 + Z13 + Z9 + Z11 + Z11 + Z14 + Z9 + Z7</f>
         <v>82</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="6">
         <v>7</v>
@@ -1994,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="6">
         <v>7</v>
@@ -2012,10 +2012,10 @@
         <v>13</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P21" s="6">
         <v>9</v>
@@ -2027,7 +2027,7 @@
         <v>11</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T21" s="6">
         <v>14</v>
@@ -2036,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W21" s="6">
         <v>7</v>
@@ -2069,32 +2069,32 @@
     </row>
     <row r="23" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="10">
         <f>Z3 + Z4 + Z4 + Z10 +Z3 + Z10 + Z12 +Z11 + Z8 + Z3 + Z6 + Z10 + 6.5 + Z5 + Z11 + Z7</f>
         <v>150.5</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="5">
         <v>3</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="6">
         <v>4</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23" s="6">
         <v>4</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6">
         <v>10</v>
@@ -2136,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
@@ -2166,14 +2166,14 @@
     </row>
     <row r="25" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="10">
         <f>Z10 + Z2 + Z5 + Z7 + Z11 + Z8 +Z7 + Z3 + Z11 +Z7 + Z8 + 5 + Z11 + Z8</f>
         <v>124</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" s="6">
         <v>10</v>
@@ -2185,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="6">
         <v>7</v>
@@ -2209,16 +2209,16 @@
         <v>7</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P25" s="6">
         <v>8</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S25" s="6">
         <v>6</v>
@@ -2263,14 +2263,14 @@
     </row>
     <row r="27" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="10">
         <f>Z8 + Z4 + Z6 + Z6 + Z5 + Z7 +Z8 + Z7 + Z10 + Z4 + Z11 + Z10</f>
         <v>108</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="6">
         <v>8</v>
@@ -2279,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="6">
         <v>6</v>
@@ -2294,7 +2294,7 @@
         <v>6</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L27" s="6">
         <v>5</v>
@@ -2315,16 +2315,16 @@
         <v>4</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V27" s="6">
         <v>11</v>
@@ -2360,14 +2360,14 @@
     </row>
     <row r="29" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="10">
         <f>Z7 + Z1 + Z7 +Z5 + Z10 + Z7 +Z6 + Z6 + Z10 +Z4 + Z11 + Z6 + Z5  + Z10 + Z4 + Z2</f>
         <v>173</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="6">
         <v>7</v>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29" s="6">
         <v>10</v>
@@ -2415,7 +2415,7 @@
         <v>5</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T29" s="6">
         <v>10</v>
@@ -2457,20 +2457,20 @@
     </row>
     <row r="31" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="10">
         <f>Z14 + Z8 + Z2 +Z4 + Z4 +Z4 + Z1 + Z6 +Z10 + Z2 + Z7 + Z10 + Z8 + 4 + Z7 + Z9</f>
         <v>173</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="6">
         <v>14</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" s="6">
         <v>8</v>
@@ -2479,7 +2479,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I31" s="6">
         <v>4</v>
@@ -2518,13 +2518,13 @@
         <v>7</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V31" s="6">
         <v>9</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
@@ -2554,20 +2554,20 @@
     </row>
     <row r="33" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="10">
         <f>Z15 + Z14 + Z10 + Z14 + Z13 + Z13 + Z12 + Z9</f>
         <v>28</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="6">
         <v>15</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F33" s="6">
         <v>14</v>
@@ -2576,13 +2576,13 @@
         <v>10</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I33" s="6">
         <v>14</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K33" s="10">
         <v>19</v>
@@ -2603,22 +2603,22 @@
         <v>13</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R33" s="6">
         <v>13</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U33" s="6">
         <v>12</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W33" s="6">
         <v>9</v>
@@ -2651,14 +2651,14 @@
     </row>
     <row r="35" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="10">
         <f>Z5 + Z9 + Z7 + Z5 + Z9 + Z5 +Z10 + Z8 +Z9 + Z12 + Z11 + Z5 + Z9 + 5.5 + Z7 + Z6</f>
         <v>128.5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" s="6">
         <v>5</v>
@@ -2667,7 +2667,7 @@
         <v>9</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35" s="6">
         <v>7</v>
@@ -2688,7 +2688,7 @@
         <v>8</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N35" s="6">
         <v>9</v>
@@ -2709,13 +2709,13 @@
         <v>5</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U35" s="6">
         <v>7</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W35" s="6">
         <v>6</v>
@@ -2748,14 +2748,14 @@
     </row>
     <row r="37" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="10">
         <f>Z11 + Z15 + Z12</f>
         <v>10</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" s="10">
         <v>18</v>
@@ -2773,7 +2773,7 @@
         <v>12</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J37" s="10">
         <v>17</v>
@@ -2785,31 +2785,31 @@
         <v>19</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N37" s="10">
         <v>17</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P37" s="10">
         <v>17</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V37" s="10">
         <v>16</v>
@@ -2845,20 +2845,20 @@
     </row>
     <row r="39" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" s="10">
         <f>Z13 + Z10 + Z8 +Z3 + Z13 + Z12 + Z12 + Z15 +Z15 + Z6 + Z12 + Z12 + 2 + Z12 + Z3</f>
         <v>86</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39" s="6">
         <v>13</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -2876,7 +2876,7 @@
         <v>12</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L39" s="6">
         <v>12</v>
@@ -2942,20 +2942,20 @@
     </row>
     <row r="41" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" s="10">
         <f>Z11 +Z13 + 3.5 + Z14 + Z11</f>
         <v>18.5</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" s="10">
         <v>20</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" s="10">
         <v>16</v>
@@ -2970,7 +2970,7 @@
         <v>18</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K41" s="10">
         <v>16</v>
@@ -2979,7 +2979,7 @@
         <v>19</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N41" s="6">
         <v>13</v>
@@ -2988,22 +2988,22 @@
         <v>19</v>
       </c>
       <c r="P41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S41" s="6">
         <v>9</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V41" s="6">
         <v>14</v>
@@ -3039,14 +3039,14 @@
     </row>
     <row r="43" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="10">
         <f>Z12 + Z8 + Z14 + Z8 + Z5 + Z15 +Z11 + Z7 + Z14 + Z5 + Z10 + Z8</f>
         <v>75</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D43" s="6">
         <v>12</v>
@@ -3055,7 +3055,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G43" s="6">
         <v>14</v>
@@ -3079,25 +3079,25 @@
         <v>14</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="10">
         <v>20</v>
       </c>
       <c r="R43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U43" s="6">
         <v>5</v>
@@ -3136,14 +3136,14 @@
     </row>
     <row r="45" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="10">
         <f>Z14 + Z13 + Z10 + 2.5 + Z14</f>
         <v>15.5</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="10">
         <v>19</v>
@@ -3161,22 +3161,22 @@
         <v>10</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45" s="10">
         <v>19</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O45" s="10">
         <v>16</v>
@@ -3185,22 +3185,22 @@
         <v>16</v>
       </c>
       <c r="Q45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S45" s="6">
         <v>11</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V45" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W45" s="6">
         <v>14</v>
@@ -3233,14 +3233,14 @@
     </row>
     <row r="47" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="10">
         <f>Z1 + Z12 + Z9 + Z1 + Z2 + Z1 + Z2 + Z1 + Z4 + Z4 + Z3 + Z1 + 10 + Z8 + Z14 + Z1 + Z5</f>
         <v>274</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -3252,10 +3252,10 @@
         <v>9</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M47" s="4">
         <v>2</v>
@@ -3330,29 +3330,29 @@
     </row>
     <row r="49" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="10">
         <f>Z13 + Z13 + Z8 + Z1 + Z15 + Z9 +Z12 + Z9 + Z14 + Z2 + Z2 + 12.5 + Z9 + Z6 + Z2 + Z1</f>
         <v>174.5</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" s="6">
         <v>13</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G49" s="6">
         <v>13</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I49" s="6">
         <v>8</v>
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L49" s="6">
         <v>15</v>
@@ -3427,32 +3427,32 @@
     </row>
     <row r="51" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="10">
         <f>Z14 + Z13 + Z13</f>
         <v>8</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="10">
         <v>21</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" s="10">
         <v>19</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J51" s="10">
         <v>20</v>
@@ -3461,28 +3461,28 @@
         <v>14</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M51" s="10">
         <v>19</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O51" s="10">
         <v>17</v>
       </c>
       <c r="P51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q51" s="6">
         <v>13</v>
       </c>
       <c r="R51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T51" s="10">
         <v>16</v>
@@ -3494,7 +3494,7 @@
         <v>13</v>
       </c>
       <c r="W51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
@@ -3524,65 +3524,65 @@
     </row>
     <row r="53" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="10">
         <f>Z13 + 1.5 + Z12</f>
         <v>8.5</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G53" s="10">
         <v>16</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I53" s="10">
         <v>20</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K53" s="10">
         <v>18</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M53" s="10">
         <v>20</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O53" s="6">
         <v>13</v>
       </c>
       <c r="P53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q53" s="10">
         <v>16</v>
       </c>
       <c r="R53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S53" s="6">
         <v>13</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U53" s="10">
         <v>18</v>
@@ -3621,44 +3621,44 @@
     </row>
     <row r="55" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55" s="10">
         <f>Z15 + Z15 + Z15 + 1 + Z15 + Z15</f>
         <v>6</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F55" s="10">
         <v>18</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I55" s="10">
         <v>21</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K55" s="6">
         <v>15</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N55" s="10">
         <v>18</v>
@@ -3667,7 +3667,7 @@
         <v>15</v>
       </c>
       <c r="P55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q55" s="6">
         <v>15</v>
@@ -3682,7 +3682,7 @@
         <v>17</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V55" s="6">
         <v>15</v>
@@ -3718,41 +3718,41 @@
     </row>
     <row r="57" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57" s="10">
         <f>Z13 + Z14 + Z14 + 3 + Z15 + Z12 + Z13</f>
         <v>18</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="10">
         <v>22</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F57" s="10">
         <v>20</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I57" s="10">
         <v>19</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K57" s="6">
         <v>13</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M57" s="10">
         <v>18</v>
@@ -3764,13 +3764,13 @@
         <v>14</v>
       </c>
       <c r="P57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q57" s="6">
         <v>14</v>
       </c>
       <c r="R57" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S57" s="6">
         <v>10</v>
@@ -3790,19 +3790,19 @@
     </row>
     <row r="59" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" s="13" t="s">
+      <c r="E59" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="20" t="s">
         <v>64</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>65</v>
       </c>
       <c r="H59" s="21"/>
       <c r="I59" s="21"/>
@@ -3818,24 +3818,24 @@
     </row>
     <row r="60" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" s="10">
         <f>B7+B9</f>
         <v>356.5</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E60" s="10">
         <f>B41+B39+B47+B49+B49+B51+B53+B43+B45+B55+B57</f>
         <v>858.5</v>
       </c>
       <c r="G60" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H60" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="I60" s="10">
         <v>274</v>
@@ -3844,10 +3844,10 @@
         <v>1</v>
       </c>
       <c r="K60" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L60" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="L60" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="M60" s="10">
         <v>128.5</v>
@@ -3856,10 +3856,10 @@
         <v>11</v>
       </c>
       <c r="O60" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P60" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="P60" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="Q60" s="10">
         <v>18</v>
@@ -3870,24 +3870,24 @@
     </row>
     <row r="61" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B61" s="10">
         <f>B11+B13</f>
         <v>259</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E61" s="10">
         <f>B69+B70+B67+B68+B63+B72</f>
         <v>1149</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="I61" s="10">
         <v>232</v>
@@ -3896,10 +3896,10 @@
         <v>2</v>
       </c>
       <c r="K61" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L61" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="M61" s="10">
         <v>124</v>
@@ -3908,10 +3908,10 @@
         <v>12</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="Q61" s="10">
         <v>15.5</v>
@@ -3922,24 +3922,24 @@
     </row>
     <row r="62" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="10">
         <f>B57+B55</f>
         <v>24</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" s="10">
         <f>B7+B9</f>
         <v>356.5</v>
       </c>
       <c r="G62" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H62" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="I62" s="10">
         <v>223</v>
@@ -3948,10 +3948,10 @@
         <v>3</v>
       </c>
       <c r="K62" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L62" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="L62" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="M62" s="10">
         <v>108</v>
@@ -3960,10 +3960,10 @@
         <v>13</v>
       </c>
       <c r="O62" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q62" s="10">
         <v>10</v>
@@ -3974,24 +3974,24 @@
     </row>
     <row r="63" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="10">
         <f>B53+B51</f>
         <v>16.5</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E63" s="10">
         <f>B61</f>
         <v>259</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="I63" s="10">
         <v>218.5</v>
@@ -4000,10 +4000,10 @@
         <v>4</v>
       </c>
       <c r="K63" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L63" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="M63" s="10">
         <v>86</v>
@@ -4012,10 +4012,10 @@
         <v>14</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="Q63" s="10">
         <v>8.5</v>
@@ -4026,24 +4026,24 @@
     </row>
     <row r="64" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" s="10">
         <f>B49+B47</f>
         <v>448.5</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E64" s="10">
         <f>B71</f>
         <v>295</v>
       </c>
       <c r="G64" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H64" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="I64" s="10">
         <v>213</v>
@@ -4052,10 +4052,10 @@
         <v>5</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M64" s="10">
         <v>82</v>
@@ -4064,10 +4064,10 @@
         <v>15</v>
       </c>
       <c r="O64" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q64" s="10">
         <v>8</v>
@@ -4078,17 +4078,17 @@
     </row>
     <row r="65" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B65" s="10">
         <f>B45+B43</f>
         <v>90.5</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I65" s="10">
         <v>174.5</v>
@@ -4097,10 +4097,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M65" s="10">
         <v>75</v>
@@ -4109,10 +4109,10 @@
         <v>16</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q65" s="10">
         <v>6</v>
@@ -4123,17 +4123,17 @@
     </row>
     <row r="66" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B66" s="10">
         <f>B41+B39</f>
         <v>104.5</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I66" s="10">
         <v>173</v>
@@ -4142,10 +4142,10 @@
         <v>7</v>
       </c>
       <c r="K66" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L66" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="L66" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="M66" s="10">
         <v>28</v>
@@ -4160,17 +4160,17 @@
     </row>
     <row r="67" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" s="10">
         <f>B37+B35</f>
         <v>138.5</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I67" s="10">
         <v>173</v>
@@ -4179,10 +4179,10 @@
         <v>8</v>
       </c>
       <c r="K67" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L67" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="L67" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="M67" s="10">
         <v>27</v>
@@ -4197,17 +4197,17 @@
     </row>
     <row r="68" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B68" s="10">
         <f>B33+B31</f>
         <v>201</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I68" s="10">
         <v>150.5</v>
@@ -4216,10 +4216,10 @@
         <v>9</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L68" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M68" s="10">
         <v>19</v>
@@ -4234,17 +4234,17 @@
     </row>
     <row r="69" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" s="10">
         <f>B29+B27</f>
         <v>281</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H69" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I69" s="14">
         <v>133.5</v>
@@ -4253,10 +4253,10 @@
         <v>10</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L69" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M69" s="10">
         <v>18.5</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="70" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B70" s="10">
         <f>B25+B23</f>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="71" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" s="10">
         <f>B21+B19</f>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="72" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B72" s="10">
         <f>B17+B15</f>
@@ -4302,256 +4302,256 @@
     </row>
     <row r="75" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="R75" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="S75" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="T75" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U75" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q75" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="R75" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="S75" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T75" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="U75" s="9" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="J76" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="K76" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="L76" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="M76" s="3" t="s">
+      <c r="N76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="N76" s="3" t="s">
+      <c r="O76" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="O76" s="3" t="s">
+      <c r="P76" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="P76" s="3" t="s">
+      <c r="Q76" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="Q76" s="3" t="s">
+      <c r="R76" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="R76" s="3" t="s">
+      <c r="S76" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="S76" s="3" t="s">
+      <c r="T76" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="T76" s="3" t="s">
+      <c r="U76" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="G78" s="3">
         <v>9</v>
       </c>
       <c r="H78" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="J78" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="K78" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="L78" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L78" s="3" t="s">
+      <c r="M78" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M78" s="3" t="s">
+      <c r="N78" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="N78" s="3" t="s">
+      <c r="O78" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="O78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="P78" s="3" t="s">
+      <c r="Q78" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="Q78" s="3" t="s">
+      <c r="R78" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="R78" s="3" t="s">
+      <c r="S78" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="S78" s="3" t="s">
+      <c r="T78" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="T78" s="3" t="s">
+      <c r="U78" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="U78" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="G80" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="H80" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="J80" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="K80" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="L80" s="3" t="s">
+      <c r="M80" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M80" s="3" t="s">
+      <c r="N80" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="N80" s="3" t="s">
+      <c r="O80" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="O80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="P80" s="3" t="s">
+      <c r="Q80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="Q80" s="3" t="s">
+      <c r="R80" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="R80" s="3" t="s">
+      <c r="S80" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="S80" s="3" t="s">
+      <c r="T80" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="T80" s="3" t="s">
+      <c r="U80" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="U80" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
